--- a/Studymaterials/中学生英作文一般動詞現在形編.xlsx
+++ b/Studymaterials/中学生英作文一般動詞現在形編.xlsx
@@ -479,7 +479,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -566,6 +566,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1010,21 +1013,22 @@
       <c r="I3" s="25" t="n"/>
       <c r="J3" s="26" t="n"/>
     </row>
-    <row r="4" ht="18" customHeight="1" s="6">
+    <row r="4" ht="36" customHeight="1" s="6">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
-        </is>
-      </c>
-      <c r="B4" s="38" t="n"/>
-      <c r="C4" s="38" t="n"/>
-      <c r="D4" s="38" t="n"/>
-      <c r="E4" s="38" t="n"/>
-      <c r="F4" s="38" t="n"/>
-      <c r="G4" s="38" t="n"/>
-      <c r="H4" s="38" t="n"/>
-      <c r="I4" s="38" t="n"/>
-      <c r="J4" s="39" t="n"/>
+          <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。
+※相手が答える形なので、返答では I / we ではなく you を使います。</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="n"/>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="32" t="n"/>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="32" t="n"/>
+      <c r="G4" s="32" t="n"/>
+      <c r="H4" s="32" t="n"/>
+      <c r="I4" s="32" t="n"/>
+      <c r="J4" s="33" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="6">
       <c r="A5" s="35" t="inlineStr">
@@ -1252,15 +1256,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B19" s="38" t="n"/>
-      <c r="C19" s="38" t="n"/>
-      <c r="D19" s="38" t="n"/>
-      <c r="E19" s="38" t="n"/>
-      <c r="F19" s="38" t="n"/>
-      <c r="G19" s="38" t="n"/>
-      <c r="H19" s="38" t="n"/>
-      <c r="I19" s="38" t="n"/>
-      <c r="J19" s="39" t="n"/>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="32" t="n"/>
+      <c r="H19" s="32" t="n"/>
+      <c r="I19" s="32" t="n"/>
+      <c r="J19" s="33" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="6">
       <c r="A20" s="34" t="inlineStr">
@@ -1488,15 +1492,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B34" s="38" t="n"/>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="38" t="n"/>
-      <c r="E34" s="38" t="n"/>
-      <c r="F34" s="38" t="n"/>
-      <c r="G34" s="38" t="n"/>
-      <c r="H34" s="38" t="n"/>
-      <c r="I34" s="38" t="n"/>
-      <c r="J34" s="39" t="n"/>
+      <c r="B34" s="32" t="n"/>
+      <c r="C34" s="32" t="n"/>
+      <c r="D34" s="32" t="n"/>
+      <c r="E34" s="32" t="n"/>
+      <c r="F34" s="32" t="n"/>
+      <c r="G34" s="32" t="n"/>
+      <c r="H34" s="32" t="n"/>
+      <c r="I34" s="32" t="n"/>
+      <c r="J34" s="33" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="6">
       <c r="A35" s="31" t="inlineStr">
@@ -1724,15 +1728,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B49" s="38" t="n"/>
-      <c r="C49" s="38" t="n"/>
-      <c r="D49" s="38" t="n"/>
-      <c r="E49" s="38" t="n"/>
-      <c r="F49" s="38" t="n"/>
-      <c r="G49" s="38" t="n"/>
-      <c r="H49" s="38" t="n"/>
-      <c r="I49" s="38" t="n"/>
-      <c r="J49" s="39" t="n"/>
+      <c r="B49" s="32" t="n"/>
+      <c r="C49" s="32" t="n"/>
+      <c r="D49" s="32" t="n"/>
+      <c r="E49" s="32" t="n"/>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="32" t="n"/>
+      <c r="H49" s="32" t="n"/>
+      <c r="I49" s="32" t="n"/>
+      <c r="J49" s="33" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1" s="6">
       <c r="A50" s="35" t="inlineStr">
@@ -1954,21 +1958,22 @@
       <c r="I63" s="25" t="n"/>
       <c r="J63" s="26" t="n"/>
     </row>
-    <row r="64" ht="18" customHeight="1" s="6">
+    <row r="64" ht="36" customHeight="1" s="6">
       <c r="A64" s="34" t="inlineStr">
         <is>
-          <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
-        </is>
-      </c>
-      <c r="B64" s="38" t="n"/>
-      <c r="C64" s="38" t="n"/>
-      <c r="D64" s="38" t="n"/>
-      <c r="E64" s="38" t="n"/>
-      <c r="F64" s="38" t="n"/>
-      <c r="G64" s="38" t="n"/>
-      <c r="H64" s="38" t="n"/>
-      <c r="I64" s="38" t="n"/>
-      <c r="J64" s="39" t="n"/>
+          <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。
+※相手が答える形なので、返答では I / we ではなく you を使います。</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="n"/>
+      <c r="C64" s="32" t="n"/>
+      <c r="D64" s="32" t="n"/>
+      <c r="E64" s="32" t="n"/>
+      <c r="F64" s="32" t="n"/>
+      <c r="G64" s="32" t="n"/>
+      <c r="H64" s="32" t="n"/>
+      <c r="I64" s="32" t="n"/>
+      <c r="J64" s="33" t="n"/>
     </row>
     <row r="65" ht="20" customHeight="1" s="6">
       <c r="A65" s="35" t="inlineStr">
@@ -2196,15 +2201,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B79" s="38" t="n"/>
-      <c r="C79" s="38" t="n"/>
-      <c r="D79" s="38" t="n"/>
-      <c r="E79" s="38" t="n"/>
-      <c r="F79" s="38" t="n"/>
-      <c r="G79" s="38" t="n"/>
-      <c r="H79" s="38" t="n"/>
-      <c r="I79" s="38" t="n"/>
-      <c r="J79" s="39" t="n"/>
+      <c r="B79" s="32" t="n"/>
+      <c r="C79" s="32" t="n"/>
+      <c r="D79" s="32" t="n"/>
+      <c r="E79" s="32" t="n"/>
+      <c r="F79" s="32" t="n"/>
+      <c r="G79" s="32" t="n"/>
+      <c r="H79" s="32" t="n"/>
+      <c r="I79" s="32" t="n"/>
+      <c r="J79" s="33" t="n"/>
     </row>
     <row r="80" ht="20" customHeight="1" s="6">
       <c r="A80" s="35" t="inlineStr">
@@ -2432,15 +2437,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B94" s="38" t="n"/>
-      <c r="C94" s="38" t="n"/>
-      <c r="D94" s="38" t="n"/>
-      <c r="E94" s="38" t="n"/>
-      <c r="F94" s="38" t="n"/>
-      <c r="G94" s="38" t="n"/>
-      <c r="H94" s="38" t="n"/>
-      <c r="I94" s="38" t="n"/>
-      <c r="J94" s="39" t="n"/>
+      <c r="B94" s="32" t="n"/>
+      <c r="C94" s="32" t="n"/>
+      <c r="D94" s="32" t="n"/>
+      <c r="E94" s="32" t="n"/>
+      <c r="F94" s="32" t="n"/>
+      <c r="G94" s="32" t="n"/>
+      <c r="H94" s="32" t="n"/>
+      <c r="I94" s="32" t="n"/>
+      <c r="J94" s="33" t="n"/>
     </row>
     <row r="95" ht="20" customHeight="1" s="6">
       <c r="A95" s="35" t="inlineStr">
@@ -2668,15 +2673,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B109" s="38" t="n"/>
-      <c r="C109" s="38" t="n"/>
-      <c r="D109" s="38" t="n"/>
-      <c r="E109" s="38" t="n"/>
-      <c r="F109" s="38" t="n"/>
-      <c r="G109" s="38" t="n"/>
-      <c r="H109" s="38" t="n"/>
-      <c r="I109" s="38" t="n"/>
-      <c r="J109" s="39" t="n"/>
+      <c r="B109" s="32" t="n"/>
+      <c r="C109" s="32" t="n"/>
+      <c r="D109" s="32" t="n"/>
+      <c r="E109" s="32" t="n"/>
+      <c r="F109" s="32" t="n"/>
+      <c r="G109" s="32" t="n"/>
+      <c r="H109" s="32" t="n"/>
+      <c r="I109" s="32" t="n"/>
+      <c r="J109" s="33" t="n"/>
     </row>
     <row r="110" ht="20" customHeight="1" s="6">
       <c r="A110" s="35" t="inlineStr">
@@ -2904,15 +2909,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B124" s="38" t="n"/>
-      <c r="C124" s="38" t="n"/>
-      <c r="D124" s="38" t="n"/>
-      <c r="E124" s="38" t="n"/>
-      <c r="F124" s="38" t="n"/>
-      <c r="G124" s="38" t="n"/>
-      <c r="H124" s="38" t="n"/>
-      <c r="I124" s="38" t="n"/>
-      <c r="J124" s="39" t="n"/>
+      <c r="B124" s="32" t="n"/>
+      <c r="C124" s="32" t="n"/>
+      <c r="D124" s="32" t="n"/>
+      <c r="E124" s="32" t="n"/>
+      <c r="F124" s="32" t="n"/>
+      <c r="G124" s="32" t="n"/>
+      <c r="H124" s="32" t="n"/>
+      <c r="I124" s="32" t="n"/>
+      <c r="J124" s="33" t="n"/>
     </row>
     <row r="125" ht="20" customHeight="1" s="6">
       <c r="A125" s="31" t="inlineStr">
@@ -3323,21 +3328,22 @@
       <c r="I3" s="25" t="n"/>
       <c r="J3" s="26" t="n"/>
     </row>
-    <row r="4" ht="18" customHeight="1" s="6">
+    <row r="4" ht="36" customHeight="1" s="6">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
-        </is>
-      </c>
-      <c r="B4" s="38" t="n"/>
-      <c r="C4" s="38" t="n"/>
-      <c r="D4" s="38" t="n"/>
-      <c r="E4" s="38" t="n"/>
-      <c r="F4" s="38" t="n"/>
-      <c r="G4" s="38" t="n"/>
-      <c r="H4" s="38" t="n"/>
-      <c r="I4" s="38" t="n"/>
-      <c r="J4" s="39" t="n"/>
+          <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。
+※相手が答える形なので、返答では I / we ではなく you を使います。</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="n"/>
+      <c r="C4" s="32" t="n"/>
+      <c r="D4" s="32" t="n"/>
+      <c r="E4" s="32" t="n"/>
+      <c r="F4" s="32" t="n"/>
+      <c r="G4" s="32" t="n"/>
+      <c r="H4" s="32" t="n"/>
+      <c r="I4" s="32" t="n"/>
+      <c r="J4" s="33" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1" s="6">
       <c r="A5" s="35" t="inlineStr">
@@ -3470,7 +3476,7 @@
     <row r="13" ht="26" customHeight="1" s="6">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>正解（返答）：Yes, I do.</t>
+          <t>正解（返答）：Yes, you do.</t>
         </is>
       </c>
       <c r="B13" s="32" t="n"/>
@@ -3502,7 +3508,7 @@
     <row r="15" ht="26" customHeight="1" s="6">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, I do not.</t>
+          <t>正解（基本形）：No, you do not.</t>
         </is>
       </c>
       <c r="B15" s="32" t="n"/>
@@ -3518,7 +3524,7 @@
     <row r="16" ht="26" customHeight="1" s="6">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, I don't.</t>
+          <t>正解（短縮形）：No, you don't.</t>
         </is>
       </c>
       <c r="B16" s="32" t="n"/>
@@ -3565,15 +3571,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B19" s="38" t="n"/>
-      <c r="C19" s="38" t="n"/>
-      <c r="D19" s="38" t="n"/>
-      <c r="E19" s="38" t="n"/>
-      <c r="F19" s="38" t="n"/>
-      <c r="G19" s="38" t="n"/>
-      <c r="H19" s="38" t="n"/>
-      <c r="I19" s="38" t="n"/>
-      <c r="J19" s="39" t="n"/>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="32" t="n"/>
+      <c r="H19" s="32" t="n"/>
+      <c r="I19" s="32" t="n"/>
+      <c r="J19" s="33" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="6">
       <c r="A20" s="34" t="inlineStr">
@@ -3801,15 +3807,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B34" s="38" t="n"/>
-      <c r="C34" s="38" t="n"/>
-      <c r="D34" s="38" t="n"/>
-      <c r="E34" s="38" t="n"/>
-      <c r="F34" s="38" t="n"/>
-      <c r="G34" s="38" t="n"/>
-      <c r="H34" s="38" t="n"/>
-      <c r="I34" s="38" t="n"/>
-      <c r="J34" s="39" t="n"/>
+      <c r="B34" s="32" t="n"/>
+      <c r="C34" s="32" t="n"/>
+      <c r="D34" s="32" t="n"/>
+      <c r="E34" s="32" t="n"/>
+      <c r="F34" s="32" t="n"/>
+      <c r="G34" s="32" t="n"/>
+      <c r="H34" s="32" t="n"/>
+      <c r="I34" s="32" t="n"/>
+      <c r="J34" s="33" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1" s="6">
       <c r="A35" s="31" t="inlineStr">
@@ -4037,15 +4043,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B49" s="38" t="n"/>
-      <c r="C49" s="38" t="n"/>
-      <c r="D49" s="38" t="n"/>
-      <c r="E49" s="38" t="n"/>
-      <c r="F49" s="38" t="n"/>
-      <c r="G49" s="38" t="n"/>
-      <c r="H49" s="38" t="n"/>
-      <c r="I49" s="38" t="n"/>
-      <c r="J49" s="39" t="n"/>
+      <c r="B49" s="32" t="n"/>
+      <c r="C49" s="32" t="n"/>
+      <c r="D49" s="32" t="n"/>
+      <c r="E49" s="32" t="n"/>
+      <c r="F49" s="32" t="n"/>
+      <c r="G49" s="32" t="n"/>
+      <c r="H49" s="32" t="n"/>
+      <c r="I49" s="32" t="n"/>
+      <c r="J49" s="33" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1" s="6">
       <c r="A50" s="35" t="inlineStr">
@@ -4267,21 +4273,22 @@
       <c r="I63" s="25" t="n"/>
       <c r="J63" s="26" t="n"/>
     </row>
-    <row r="64" ht="18" customHeight="1" s="6">
+    <row r="64" ht="36" customHeight="1" s="6">
       <c r="A64" s="34" t="inlineStr">
         <is>
-          <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
-        </is>
-      </c>
-      <c r="B64" s="38" t="n"/>
-      <c r="C64" s="38" t="n"/>
-      <c r="D64" s="38" t="n"/>
-      <c r="E64" s="38" t="n"/>
-      <c r="F64" s="38" t="n"/>
-      <c r="G64" s="38" t="n"/>
-      <c r="H64" s="38" t="n"/>
-      <c r="I64" s="38" t="n"/>
-      <c r="J64" s="39" t="n"/>
+          <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。
+※相手が答える形なので、返答では I / we ではなく you を使います。</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="n"/>
+      <c r="C64" s="32" t="n"/>
+      <c r="D64" s="32" t="n"/>
+      <c r="E64" s="32" t="n"/>
+      <c r="F64" s="32" t="n"/>
+      <c r="G64" s="32" t="n"/>
+      <c r="H64" s="32" t="n"/>
+      <c r="I64" s="32" t="n"/>
+      <c r="J64" s="33" t="n"/>
     </row>
     <row r="65" ht="20" customHeight="1" s="6">
       <c r="A65" s="35" t="inlineStr">
@@ -4414,7 +4421,7 @@
     <row r="73" ht="26" customHeight="1" s="6">
       <c r="A73" s="34" t="inlineStr">
         <is>
-          <t>正解（返答）：Yes, we do.</t>
+          <t>正解（返答）：Yes, you do.</t>
         </is>
       </c>
       <c r="B73" s="32" t="n"/>
@@ -4446,7 +4453,7 @@
     <row r="75" ht="26" customHeight="1" s="6">
       <c r="A75" s="35" t="inlineStr">
         <is>
-          <t>正解（基本形）：No, we do not.</t>
+          <t>正解（基本形）：No, you do not.</t>
         </is>
       </c>
       <c r="B75" s="32" t="n"/>
@@ -4462,7 +4469,7 @@
     <row r="76" ht="26" customHeight="1" s="6">
       <c r="A76" s="35" t="inlineStr">
         <is>
-          <t>正解（短縮形）：No, we don't.</t>
+          <t>正解（短縮形）：No, you don't.</t>
         </is>
       </c>
       <c r="B76" s="32" t="n"/>
@@ -4509,15 +4516,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B79" s="38" t="n"/>
-      <c r="C79" s="38" t="n"/>
-      <c r="D79" s="38" t="n"/>
-      <c r="E79" s="38" t="n"/>
-      <c r="F79" s="38" t="n"/>
-      <c r="G79" s="38" t="n"/>
-      <c r="H79" s="38" t="n"/>
-      <c r="I79" s="38" t="n"/>
-      <c r="J79" s="39" t="n"/>
+      <c r="B79" s="32" t="n"/>
+      <c r="C79" s="32" t="n"/>
+      <c r="D79" s="32" t="n"/>
+      <c r="E79" s="32" t="n"/>
+      <c r="F79" s="32" t="n"/>
+      <c r="G79" s="32" t="n"/>
+      <c r="H79" s="32" t="n"/>
+      <c r="I79" s="32" t="n"/>
+      <c r="J79" s="33" t="n"/>
     </row>
     <row r="80" ht="20" customHeight="1" s="6">
       <c r="A80" s="35" t="inlineStr">
@@ -4745,15 +4752,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B94" s="38" t="n"/>
-      <c r="C94" s="38" t="n"/>
-      <c r="D94" s="38" t="n"/>
-      <c r="E94" s="38" t="n"/>
-      <c r="F94" s="38" t="n"/>
-      <c r="G94" s="38" t="n"/>
-      <c r="H94" s="38" t="n"/>
-      <c r="I94" s="38" t="n"/>
-      <c r="J94" s="39" t="n"/>
+      <c r="B94" s="32" t="n"/>
+      <c r="C94" s="32" t="n"/>
+      <c r="D94" s="32" t="n"/>
+      <c r="E94" s="32" t="n"/>
+      <c r="F94" s="32" t="n"/>
+      <c r="G94" s="32" t="n"/>
+      <c r="H94" s="32" t="n"/>
+      <c r="I94" s="32" t="n"/>
+      <c r="J94" s="33" t="n"/>
     </row>
     <row r="95" ht="20" customHeight="1" s="6">
       <c r="A95" s="35" t="inlineStr">
@@ -4981,15 +4988,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B109" s="38" t="n"/>
-      <c r="C109" s="38" t="n"/>
-      <c r="D109" s="38" t="n"/>
-      <c r="E109" s="38" t="n"/>
-      <c r="F109" s="38" t="n"/>
-      <c r="G109" s="38" t="n"/>
-      <c r="H109" s="38" t="n"/>
-      <c r="I109" s="38" t="n"/>
-      <c r="J109" s="39" t="n"/>
+      <c r="B109" s="32" t="n"/>
+      <c r="C109" s="32" t="n"/>
+      <c r="D109" s="32" t="n"/>
+      <c r="E109" s="32" t="n"/>
+      <c r="F109" s="32" t="n"/>
+      <c r="G109" s="32" t="n"/>
+      <c r="H109" s="32" t="n"/>
+      <c r="I109" s="32" t="n"/>
+      <c r="J109" s="33" t="n"/>
     </row>
     <row r="110" ht="20" customHeight="1" s="6">
       <c r="A110" s="35" t="inlineStr">
@@ -5217,15 +5224,15 @@
           <t>※否定文では do not / does not、短縮形では don't / doesn't を使います。</t>
         </is>
       </c>
-      <c r="B124" s="38" t="n"/>
-      <c r="C124" s="38" t="n"/>
-      <c r="D124" s="38" t="n"/>
-      <c r="E124" s="38" t="n"/>
-      <c r="F124" s="38" t="n"/>
-      <c r="G124" s="38" t="n"/>
-      <c r="H124" s="38" t="n"/>
-      <c r="I124" s="38" t="n"/>
-      <c r="J124" s="39" t="n"/>
+      <c r="B124" s="32" t="n"/>
+      <c r="C124" s="32" t="n"/>
+      <c r="D124" s="32" t="n"/>
+      <c r="E124" s="32" t="n"/>
+      <c r="F124" s="32" t="n"/>
+      <c r="G124" s="32" t="n"/>
+      <c r="H124" s="32" t="n"/>
+      <c r="I124" s="32" t="n"/>
+      <c r="J124" s="33" t="n"/>
     </row>
     <row r="125" ht="20" customHeight="1" s="6">
       <c r="A125" s="31" t="inlineStr">
